--- a/Resincraftcode-molds-and-materials.xlsx
+++ b/Resincraftcode-molds-and-materials.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decorations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glitter, tassels, letters" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epoxy colours" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All my photos" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -217,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -255,6 +256,9 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -354,6 +358,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -379,6 +386,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -404,6 +414,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -429,6 +442,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -454,6 +470,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -479,6 +498,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -504,6 +526,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -529,6 +554,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -554,6 +582,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -579,6 +610,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -604,6 +638,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -629,6 +666,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -654,6 +694,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -679,6 +722,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -704,6 +750,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -729,6 +778,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -754,6 +806,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -779,6 +834,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -804,6 +862,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -829,6 +890,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -854,6 +918,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -879,6 +946,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -904,6 +974,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -929,6 +1002,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -954,6 +1030,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -979,6 +1058,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1004,6 +1086,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1029,6 +1114,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1054,6 +1142,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1079,6 +1170,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1104,6 +1198,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1129,6 +1226,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1154,6 +1254,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1179,6 +1282,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1204,6 +1310,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1229,6 +1338,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1254,6 +1366,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1279,6 +1394,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1304,6 +1422,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1329,6 +1450,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1354,6 +1478,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1379,6 +1506,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1409,6 +1539,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1434,6 +1567,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1459,6 +1595,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1484,6 +1623,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1509,6 +1651,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1534,6 +1679,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1559,6 +1707,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1584,6 +1735,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1609,6 +1763,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1634,6 +1791,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1659,6 +1819,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1684,6 +1847,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1709,6 +1875,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1734,6 +1903,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1759,6 +1931,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1784,6 +1959,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1809,6 +1987,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1834,6 +2015,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1859,6 +2043,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1884,6 +2071,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1909,6 +2099,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1934,6 +2127,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1959,6 +2155,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1984,6 +2183,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2009,6 +2211,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2034,6 +2239,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2059,6 +2267,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2084,6 +2295,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2109,6 +2323,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2134,6 +2351,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2159,6 +2379,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2184,6 +2407,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2209,6 +2435,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2234,6 +2463,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2259,6 +2491,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2284,6 +2519,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2309,6 +2547,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2334,6 +2575,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2359,6 +2603,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2384,6 +2631,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2409,6 +2659,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2434,6 +2687,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2459,6 +2715,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2484,6 +2743,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2509,6 +2771,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2534,6 +2799,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2559,6 +2827,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2584,6 +2855,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2609,6 +2883,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2634,6 +2911,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2659,6 +2939,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2684,6 +2967,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2709,6 +2995,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2734,6 +3023,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2759,6 +3051,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2784,6 +3079,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2809,6 +3107,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2834,6 +3135,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2859,6 +3163,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2884,6 +3191,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2909,6 +3219,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2934,6 +3247,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2959,6 +3275,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2984,6 +3303,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3009,6 +3331,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3034,6 +3359,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3059,6 +3387,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3084,6 +3415,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3109,6 +3443,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3134,6 +3471,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3159,6 +3499,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3184,6 +3527,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3209,6 +3555,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3234,6 +3583,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3259,6 +3611,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3284,6 +3639,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3309,6 +3667,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3334,6 +3695,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3359,6 +3723,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3384,6 +3751,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3409,6 +3779,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3434,6 +3807,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3459,6 +3835,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3484,6 +3863,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3509,6 +3891,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3534,6 +3919,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3559,6 +3947,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3584,6 +3975,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3609,6 +4003,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3634,6 +4031,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3659,6 +4059,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3684,6 +4087,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3709,6 +4115,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3734,6 +4143,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3759,6 +4171,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3784,6 +4199,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3809,6 +4227,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3834,6 +4255,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3859,6 +4283,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3884,6 +4311,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3909,6 +4339,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3934,6 +4367,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3959,6 +4395,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3989,6 +4428,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4014,6 +4456,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4039,6 +4484,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4064,6 +4512,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4089,6 +4540,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4114,6 +4568,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4139,6 +4596,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4164,6 +4624,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4189,6 +4652,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4214,6 +4680,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4239,6 +4708,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4264,6 +4736,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4289,6 +4764,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4314,6 +4792,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4339,6 +4820,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4364,6 +4848,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4389,6 +4876,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4414,6 +4904,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4439,6 +4932,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4464,6 +4960,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4489,6 +4988,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4514,6 +5016,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4539,6 +5044,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4564,6 +5072,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4589,6 +5100,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4614,6 +5128,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4639,6 +5156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4664,6 +5184,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4689,6 +5212,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4714,6 +5240,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4739,6 +5268,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4764,6 +5296,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4789,6 +5324,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4814,6 +5352,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4833,6 +5374,3739 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>74</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>79</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>81</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>82</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>84</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>89</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>90</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>91</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>92</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>96</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>105</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId109"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>110</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="110" name="Image 110" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId110"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>111</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="111" name="Image 111" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId111"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="112" name="Image 112" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>113</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId113"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId114"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="115" name="Image 115" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId115"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>116</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="116" name="Image 116" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId116"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>117</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="117" name="Image 117" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId117"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>118</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="118" name="Image 118" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId118"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>119</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="119" name="Image 119" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId119"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>120</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="120" name="Image 120" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId120"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>121</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="121" name="Image 121" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>122</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="122" name="Image 122" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId122"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>123</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="123" name="Image 123" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId123"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>124</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="124" name="Image 124" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId124"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>125</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="125" name="Image 125" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId125"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>126</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="126" name="Image 126" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId126"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>127</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="127" name="Image 127" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId127"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="128" name="Image 128" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId128"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>129</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="129" name="Image 129" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId129"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="130" name="Image 130" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId130"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>131</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="131" name="Image 131" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId131"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>132</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="132" name="Image 132" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId132"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>133</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="133" name="Image 133" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId133"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>134</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="134" name="Image 134" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId134"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>135</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="135" name="Image 135" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId135"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>136</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="136" name="Image 136" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId136"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>137</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1076325" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="137" name="Image 137" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId137"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>138</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1200150" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="138" name="Image 138" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId138"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>139</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="139" name="Image 139" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId139"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>140</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="140" name="Image 140" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId140"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>141</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="141" name="Image 141" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId141"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>142</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="142" name="Image 142" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId142"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>143</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="143" name="Image 143" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId143"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>144</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1181100" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="144" name="Image 144" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId144"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="145" name="Image 145" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId145"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>146</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="146" name="Image 146" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId146"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>147</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="147" name="Image 147" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId147"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>148</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1114425" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="148" name="Image 148" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId148"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>149</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="149" name="Image 149" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId149"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5148,9 +9422,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -12307,9 +16579,6 @@
           <t>#2F4FB5</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12328,9 +16597,6 @@
           <t>#1C6FC9</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12349,9 +16615,6 @@
           <t>#4F9BE0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12370,9 +16633,6 @@
           <t>#2C93A8</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12391,9 +16651,6 @@
           <t>#29B7A3</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12412,9 +16669,6 @@
           <t>#7CCFB6</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12433,9 +16687,6 @@
           <t>#2F5A4C</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12454,9 +16705,6 @@
           <t>#1E1E20</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12475,9 +16723,6 @@
           <t>#4A4C4A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12496,9 +16741,6 @@
           <t>#7C7B76</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12517,9 +16759,6 @@
           <t>#C9C9CB</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12538,9 +16777,6 @@
           <t>#EFEAE6</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12559,9 +16795,6 @@
           <t>#D9C2A8</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12580,9 +16813,6 @@
           <t>#D4A93C</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12601,9 +16831,6 @@
           <t>#C9B04E</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12622,9 +16849,6 @@
           <t>#9A7A2E</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12643,9 +16867,6 @@
           <t>#A56B3E</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12664,9 +16885,6 @@
           <t>#C07445</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12685,9 +16903,6 @@
           <t>#C98B6E</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12706,9 +16921,6 @@
           <t>#E0792F</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12727,9 +16939,6 @@
           <t>#D05563</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12748,9 +16957,6 @@
           <t>#C45160</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12769,9 +16975,6 @@
           <t>#EBA3B0</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12790,9 +16993,6 @@
           <t>#E58FA6</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12811,9 +17011,6 @@
           <t>#F2C3CE</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12832,9 +17029,6 @@
           <t>#B2467D</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12853,9 +17047,6 @@
           <t>#5A63C4</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12874,9 +17065,6 @@
           <t>#7E4FB5</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Colour was matched by eye from the bottle cap — please check.</t>
@@ -12886,4 +17074,2145 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F150"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>File name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>What it shows (you fill in)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Used in the app?</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="115" customHeight="1">
+      <c r="A2" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="33" t="inlineStr"/>
+      <c r="C2" s="33" t="inlineStr">
+        <is>
+          <t>58c79970-image.jpg</t>
+        </is>
+      </c>
+      <c r="D2" s="33" t="inlineStr"/>
+      <c r="E2" s="33" t="inlineStr"/>
+      <c r="F2" s="33" t="inlineStr"/>
+    </row>
+    <row r="3" ht="115" customHeight="1">
+      <c r="A3" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="33" t="inlineStr"/>
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>071a58eb-image.jpg</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="inlineStr"/>
+      <c r="E3" s="33" t="inlineStr"/>
+      <c r="F3" s="33" t="inlineStr"/>
+    </row>
+    <row r="4" ht="115" customHeight="1">
+      <c r="A4" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="33" t="inlineStr"/>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>cf4eeff3-image.jpg</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr"/>
+      <c r="E4" s="33" t="inlineStr"/>
+      <c r="F4" s="33" t="inlineStr"/>
+    </row>
+    <row r="5" ht="115" customHeight="1">
+      <c r="A5" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="33" t="inlineStr"/>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>bff25939-image.jpg</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr"/>
+      <c r="E5" s="33" t="inlineStr"/>
+      <c r="F5" s="33" t="inlineStr"/>
+    </row>
+    <row r="6" ht="115" customHeight="1">
+      <c r="A6" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="33" t="inlineStr"/>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>28ae6926-image.jpg</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr"/>
+      <c r="E6" s="33" t="inlineStr"/>
+      <c r="F6" s="33" t="inlineStr"/>
+    </row>
+    <row r="7" ht="115" customHeight="1">
+      <c r="A7" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="33" t="inlineStr"/>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>03711fee-image.jpg</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr"/>
+      <c r="E7" s="33" t="inlineStr"/>
+      <c r="F7" s="33" t="inlineStr"/>
+    </row>
+    <row r="8" ht="115" customHeight="1">
+      <c r="A8" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="33" t="inlineStr"/>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>83162d58-image.jpg</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr"/>
+      <c r="E8" s="33" t="inlineStr"/>
+      <c r="F8" s="33" t="inlineStr"/>
+    </row>
+    <row r="9" ht="115" customHeight="1">
+      <c r="A9" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="33" t="inlineStr"/>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>75213834-image.jpg</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr"/>
+      <c r="E9" s="33" t="inlineStr"/>
+      <c r="F9" s="33" t="inlineStr"/>
+    </row>
+    <row r="10" ht="115" customHeight="1">
+      <c r="A10" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="33" t="inlineStr"/>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>17f189c8-image.jpg</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr"/>
+      <c r="E10" s="33" t="inlineStr"/>
+      <c r="F10" s="33" t="inlineStr"/>
+    </row>
+    <row r="11" ht="115" customHeight="1">
+      <c r="A11" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="33" t="inlineStr"/>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>136246d9-image.jpg</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr"/>
+      <c r="E11" s="33" t="inlineStr"/>
+      <c r="F11" s="33" t="inlineStr"/>
+    </row>
+    <row r="12" ht="115" customHeight="1">
+      <c r="A12" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="33" t="inlineStr"/>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>6328c73f-image.jpg</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr"/>
+      <c r="E12" s="33" t="inlineStr"/>
+      <c r="F12" s="33" t="inlineStr"/>
+    </row>
+    <row r="13" ht="115" customHeight="1">
+      <c r="A13" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="33" t="inlineStr"/>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>6590336b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr"/>
+      <c r="E13" s="33" t="inlineStr"/>
+      <c r="F13" s="33" t="inlineStr"/>
+    </row>
+    <row r="14" ht="115" customHeight="1">
+      <c r="A14" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="33" t="inlineStr"/>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>a1b2fe27-image.jpg</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="inlineStr"/>
+      <c r="E14" s="33" t="inlineStr"/>
+      <c r="F14" s="33" t="inlineStr"/>
+    </row>
+    <row r="15" ht="115" customHeight="1">
+      <c r="A15" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="33" t="inlineStr"/>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>86a7ef0b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr"/>
+      <c r="E15" s="33" t="inlineStr"/>
+      <c r="F15" s="33" t="inlineStr"/>
+    </row>
+    <row r="16" ht="115" customHeight="1">
+      <c r="A16" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="33" t="inlineStr"/>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>c38c1886-image.jpg</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr"/>
+      <c r="E16" s="33" t="inlineStr"/>
+      <c r="F16" s="33" t="inlineStr"/>
+    </row>
+    <row r="17" ht="115" customHeight="1">
+      <c r="A17" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="33" t="inlineStr"/>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>c1abc3e4-image.jpg</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr"/>
+      <c r="E17" s="33" t="inlineStr"/>
+      <c r="F17" s="33" t="inlineStr"/>
+    </row>
+    <row r="18" ht="115" customHeight="1">
+      <c r="A18" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="33" t="inlineStr"/>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>5e4cc8c0-image.jpg</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr"/>
+      <c r="E18" s="33" t="inlineStr"/>
+      <c r="F18" s="33" t="inlineStr"/>
+    </row>
+    <row r="19" ht="115" customHeight="1">
+      <c r="A19" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="33" t="inlineStr"/>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>20193a84-image.jpg</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr"/>
+      <c r="E19" s="33" t="inlineStr"/>
+      <c r="F19" s="33" t="inlineStr"/>
+    </row>
+    <row r="20" ht="115" customHeight="1">
+      <c r="A20" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="33" t="inlineStr"/>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>9a3072e8-image.jpg</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr"/>
+      <c r="E20" s="33" t="inlineStr"/>
+      <c r="F20" s="33" t="inlineStr"/>
+    </row>
+    <row r="21" ht="115" customHeight="1">
+      <c r="A21" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="33" t="inlineStr"/>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>32aa199b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr"/>
+      <c r="E21" s="33" t="inlineStr"/>
+      <c r="F21" s="33" t="inlineStr"/>
+    </row>
+    <row r="22" ht="115" customHeight="1">
+      <c r="A22" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="33" t="inlineStr"/>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>43581cd1-image.jpg</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr"/>
+      <c r="E22" s="33" t="inlineStr"/>
+      <c r="F22" s="33" t="inlineStr"/>
+    </row>
+    <row r="23" ht="115" customHeight="1">
+      <c r="A23" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="33" t="inlineStr"/>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>7a0c237a-image.jpg</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr"/>
+      <c r="E23" s="33" t="inlineStr"/>
+      <c r="F23" s="33" t="inlineStr"/>
+    </row>
+    <row r="24" ht="115" customHeight="1">
+      <c r="A24" s="33" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="33" t="inlineStr"/>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>cd51346b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr"/>
+      <c r="E24" s="33" t="inlineStr"/>
+      <c r="F24" s="33" t="inlineStr"/>
+    </row>
+    <row r="25" ht="115" customHeight="1">
+      <c r="A25" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="33" t="inlineStr"/>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>85d30016-image.jpg</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr"/>
+      <c r="E25" s="33" t="inlineStr"/>
+      <c r="F25" s="33" t="inlineStr"/>
+    </row>
+    <row r="26" ht="115" customHeight="1">
+      <c r="A26" s="33" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="33" t="inlineStr"/>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>cbe60dee-image.jpg</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr"/>
+      <c r="E26" s="33" t="inlineStr"/>
+      <c r="F26" s="33" t="inlineStr"/>
+    </row>
+    <row r="27" ht="115" customHeight="1">
+      <c r="A27" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="33" t="inlineStr"/>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>8db4005a-image.jpg</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="inlineStr"/>
+      <c r="E27" s="33" t="inlineStr"/>
+      <c r="F27" s="33" t="inlineStr"/>
+    </row>
+    <row r="28" ht="115" customHeight="1">
+      <c r="A28" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="33" t="inlineStr"/>
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>3fcbd29e-image.jpg</t>
+        </is>
+      </c>
+      <c r="D28" s="33" t="inlineStr"/>
+      <c r="E28" s="33" t="inlineStr"/>
+      <c r="F28" s="33" t="inlineStr"/>
+    </row>
+    <row r="29" ht="115" customHeight="1">
+      <c r="A29" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="33" t="inlineStr"/>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>187d0b55-image.jpg</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr"/>
+      <c r="E29" s="33" t="inlineStr"/>
+      <c r="F29" s="33" t="inlineStr"/>
+    </row>
+    <row r="30" ht="115" customHeight="1">
+      <c r="A30" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="33" t="inlineStr"/>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>36561564-image.jpg</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr"/>
+      <c r="E30" s="33" t="inlineStr"/>
+      <c r="F30" s="33" t="inlineStr"/>
+    </row>
+    <row r="31" ht="115" customHeight="1">
+      <c r="A31" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="33" t="inlineStr"/>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>bda46154-image.jpg</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="inlineStr"/>
+      <c r="E31" s="33" t="inlineStr"/>
+      <c r="F31" s="33" t="inlineStr"/>
+    </row>
+    <row r="32" ht="115" customHeight="1">
+      <c r="A32" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="33" t="inlineStr"/>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>13090650-image.jpg</t>
+        </is>
+      </c>
+      <c r="D32" s="33" t="inlineStr"/>
+      <c r="E32" s="33" t="inlineStr"/>
+      <c r="F32" s="33" t="inlineStr"/>
+    </row>
+    <row r="33" ht="115" customHeight="1">
+      <c r="A33" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="33" t="inlineStr"/>
+      <c r="C33" s="33" t="inlineStr">
+        <is>
+          <t>a607e26b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr"/>
+      <c r="E33" s="33" t="inlineStr"/>
+      <c r="F33" s="33" t="inlineStr"/>
+    </row>
+    <row r="34" ht="115" customHeight="1">
+      <c r="A34" s="33" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="33" t="inlineStr"/>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>abe432eb-image.jpg</t>
+        </is>
+      </c>
+      <c r="D34" s="33" t="inlineStr"/>
+      <c r="E34" s="33" t="inlineStr"/>
+      <c r="F34" s="33" t="inlineStr"/>
+    </row>
+    <row r="35" ht="115" customHeight="1">
+      <c r="A35" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="33" t="inlineStr"/>
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>fa22a46c-image.jpg</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="inlineStr"/>
+      <c r="E35" s="33" t="inlineStr"/>
+      <c r="F35" s="33" t="inlineStr"/>
+    </row>
+    <row r="36" ht="115" customHeight="1">
+      <c r="A36" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="33" t="inlineStr"/>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>35546c40-image.jpg</t>
+        </is>
+      </c>
+      <c r="D36" s="33" t="inlineStr"/>
+      <c r="E36" s="33" t="inlineStr"/>
+      <c r="F36" s="33" t="inlineStr"/>
+    </row>
+    <row r="37" ht="115" customHeight="1">
+      <c r="A37" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="33" t="inlineStr"/>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>1f179bf3-image.jpg</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="inlineStr"/>
+      <c r="E37" s="33" t="inlineStr"/>
+      <c r="F37" s="33" t="inlineStr"/>
+    </row>
+    <row r="38" ht="115" customHeight="1">
+      <c r="A38" s="33" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="33" t="inlineStr"/>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>ba8792be-image.jpg</t>
+        </is>
+      </c>
+      <c r="D38" s="33" t="inlineStr"/>
+      <c r="E38" s="33" t="inlineStr"/>
+      <c r="F38" s="33" t="inlineStr"/>
+    </row>
+    <row r="39" ht="115" customHeight="1">
+      <c r="A39" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="33" t="inlineStr"/>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>2b9b1ec5-image.jpg</t>
+        </is>
+      </c>
+      <c r="D39" s="33" t="inlineStr"/>
+      <c r="E39" s="33" t="inlineStr"/>
+      <c r="F39" s="33" t="inlineStr"/>
+    </row>
+    <row r="40" ht="115" customHeight="1">
+      <c r="A40" s="33" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="33" t="inlineStr"/>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>90edfec2-image.jpg</t>
+        </is>
+      </c>
+      <c r="D40" s="33" t="inlineStr"/>
+      <c r="E40" s="33" t="inlineStr"/>
+      <c r="F40" s="33" t="inlineStr"/>
+    </row>
+    <row r="41" ht="115" customHeight="1">
+      <c r="A41" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="33" t="inlineStr"/>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>3bbe2415-image.jpg</t>
+        </is>
+      </c>
+      <c r="D41" s="33" t="inlineStr"/>
+      <c r="E41" s="33" t="inlineStr"/>
+      <c r="F41" s="33" t="inlineStr"/>
+    </row>
+    <row r="42" ht="115" customHeight="1">
+      <c r="A42" s="33" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="33" t="inlineStr"/>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>3599cdb2-image.jpg</t>
+        </is>
+      </c>
+      <c r="D42" s="33" t="inlineStr"/>
+      <c r="E42" s="33" t="inlineStr"/>
+      <c r="F42" s="33" t="inlineStr"/>
+    </row>
+    <row r="43" ht="115" customHeight="1">
+      <c r="A43" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="33" t="inlineStr"/>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>0241540a-image.jpg</t>
+        </is>
+      </c>
+      <c r="D43" s="33" t="inlineStr"/>
+      <c r="E43" s="33" t="inlineStr"/>
+      <c r="F43" s="33" t="inlineStr"/>
+    </row>
+    <row r="44" ht="115" customHeight="1">
+      <c r="A44" s="33" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="33" t="inlineStr"/>
+      <c r="C44" s="33" t="inlineStr">
+        <is>
+          <t>1fd4ab7b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr"/>
+      <c r="E44" s="33" t="inlineStr"/>
+      <c r="F44" s="33" t="inlineStr"/>
+    </row>
+    <row r="45" ht="115" customHeight="1">
+      <c r="A45" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="33" t="inlineStr"/>
+      <c r="C45" s="33" t="inlineStr">
+        <is>
+          <t>61ef81d9-image.jpg</t>
+        </is>
+      </c>
+      <c r="D45" s="33" t="inlineStr"/>
+      <c r="E45" s="33" t="inlineStr"/>
+      <c r="F45" s="33" t="inlineStr"/>
+    </row>
+    <row r="46" ht="115" customHeight="1">
+      <c r="A46" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="33" t="inlineStr"/>
+      <c r="C46" s="33" t="inlineStr">
+        <is>
+          <t>2c824bce-image.jpg</t>
+        </is>
+      </c>
+      <c r="D46" s="33" t="inlineStr"/>
+      <c r="E46" s="33" t="inlineStr"/>
+      <c r="F46" s="33" t="inlineStr"/>
+    </row>
+    <row r="47" ht="115" customHeight="1">
+      <c r="A47" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="33" t="inlineStr"/>
+      <c r="C47" s="33" t="inlineStr">
+        <is>
+          <t>d185a59c-image.jpg</t>
+        </is>
+      </c>
+      <c r="D47" s="33" t="inlineStr"/>
+      <c r="E47" s="33" t="inlineStr"/>
+      <c r="F47" s="33" t="inlineStr"/>
+    </row>
+    <row r="48" ht="115" customHeight="1">
+      <c r="A48" s="33" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="33" t="inlineStr"/>
+      <c r="C48" s="33" t="inlineStr">
+        <is>
+          <t>bc2f78fd-image.jpg</t>
+        </is>
+      </c>
+      <c r="D48" s="33" t="inlineStr"/>
+      <c r="E48" s="33" t="inlineStr"/>
+      <c r="F48" s="33" t="inlineStr"/>
+    </row>
+    <row r="49" ht="115" customHeight="1">
+      <c r="A49" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="33" t="inlineStr"/>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>eee018c7-image.jpg</t>
+        </is>
+      </c>
+      <c r="D49" s="33" t="inlineStr"/>
+      <c r="E49" s="33" t="inlineStr"/>
+      <c r="F49" s="33" t="inlineStr"/>
+    </row>
+    <row r="50" ht="115" customHeight="1">
+      <c r="A50" s="33" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="33" t="inlineStr"/>
+      <c r="C50" s="33" t="inlineStr">
+        <is>
+          <t>83c12bf9-image.jpg</t>
+        </is>
+      </c>
+      <c r="D50" s="33" t="inlineStr"/>
+      <c r="E50" s="33" t="inlineStr"/>
+      <c r="F50" s="33" t="inlineStr"/>
+    </row>
+    <row r="51" ht="115" customHeight="1">
+      <c r="A51" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="33" t="inlineStr"/>
+      <c r="C51" s="33" t="inlineStr">
+        <is>
+          <t>ab13e978-image.jpg</t>
+        </is>
+      </c>
+      <c r="D51" s="33" t="inlineStr"/>
+      <c r="E51" s="33" t="inlineStr"/>
+      <c r="F51" s="33" t="inlineStr"/>
+    </row>
+    <row r="52" ht="115" customHeight="1">
+      <c r="A52" s="33" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="33" t="inlineStr"/>
+      <c r="C52" s="33" t="inlineStr">
+        <is>
+          <t>ccbe59f6-image.jpg</t>
+        </is>
+      </c>
+      <c r="D52" s="33" t="inlineStr"/>
+      <c r="E52" s="33" t="inlineStr"/>
+      <c r="F52" s="33" t="inlineStr"/>
+    </row>
+    <row r="53" ht="115" customHeight="1">
+      <c r="A53" s="33" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="33" t="inlineStr"/>
+      <c r="C53" s="33" t="inlineStr">
+        <is>
+          <t>bd4c0608-image.jpg</t>
+        </is>
+      </c>
+      <c r="D53" s="33" t="inlineStr"/>
+      <c r="E53" s="33" t="inlineStr"/>
+      <c r="F53" s="33" t="inlineStr"/>
+    </row>
+    <row r="54" ht="115" customHeight="1">
+      <c r="A54" s="33" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="33" t="inlineStr"/>
+      <c r="C54" s="33" t="inlineStr">
+        <is>
+          <t>0cd099bb-image.jpg</t>
+        </is>
+      </c>
+      <c r="D54" s="33" t="inlineStr"/>
+      <c r="E54" s="33" t="inlineStr"/>
+      <c r="F54" s="33" t="inlineStr"/>
+    </row>
+    <row r="55" ht="115" customHeight="1">
+      <c r="A55" s="33" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="33" t="inlineStr"/>
+      <c r="C55" s="33" t="inlineStr">
+        <is>
+          <t>59708afe-image.jpg</t>
+        </is>
+      </c>
+      <c r="D55" s="33" t="inlineStr"/>
+      <c r="E55" s="33" t="inlineStr"/>
+      <c r="F55" s="33" t="inlineStr"/>
+    </row>
+    <row r="56" ht="115" customHeight="1">
+      <c r="A56" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="33" t="inlineStr"/>
+      <c r="C56" s="33" t="inlineStr">
+        <is>
+          <t>2817f118-image.jpg</t>
+        </is>
+      </c>
+      <c r="D56" s="33" t="inlineStr"/>
+      <c r="E56" s="33" t="inlineStr"/>
+      <c r="F56" s="33" t="inlineStr"/>
+    </row>
+    <row r="57" ht="115" customHeight="1">
+      <c r="A57" s="33" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="33" t="inlineStr"/>
+      <c r="C57" s="33" t="inlineStr">
+        <is>
+          <t>f046cd7c-image.jpg</t>
+        </is>
+      </c>
+      <c r="D57" s="33" t="inlineStr"/>
+      <c r="E57" s="33" t="inlineStr"/>
+      <c r="F57" s="33" t="inlineStr"/>
+    </row>
+    <row r="58" ht="115" customHeight="1">
+      <c r="A58" s="33" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="33" t="inlineStr"/>
+      <c r="C58" s="33" t="inlineStr">
+        <is>
+          <t>bd0e030a-image.jpg</t>
+        </is>
+      </c>
+      <c r="D58" s="33" t="inlineStr"/>
+      <c r="E58" s="33" t="inlineStr"/>
+      <c r="F58" s="33" t="inlineStr"/>
+    </row>
+    <row r="59" ht="115" customHeight="1">
+      <c r="A59" s="33" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="33" t="inlineStr"/>
+      <c r="C59" s="33" t="inlineStr">
+        <is>
+          <t>c5ed3709-image.jpg</t>
+        </is>
+      </c>
+      <c r="D59" s="33" t="inlineStr"/>
+      <c r="E59" s="33" t="inlineStr"/>
+      <c r="F59" s="33" t="inlineStr"/>
+    </row>
+    <row r="60" ht="115" customHeight="1">
+      <c r="A60" s="33" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="33" t="inlineStr"/>
+      <c r="C60" s="33" t="inlineStr">
+        <is>
+          <t>cf93fbee-image.jpg</t>
+        </is>
+      </c>
+      <c r="D60" s="33" t="inlineStr"/>
+      <c r="E60" s="33" t="inlineStr"/>
+      <c r="F60" s="33" t="inlineStr"/>
+    </row>
+    <row r="61" ht="115" customHeight="1">
+      <c r="A61" s="33" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="33" t="inlineStr"/>
+      <c r="C61" s="33" t="inlineStr">
+        <is>
+          <t>74e073d3-image.jpg</t>
+        </is>
+      </c>
+      <c r="D61" s="33" t="inlineStr"/>
+      <c r="E61" s="33" t="inlineStr"/>
+      <c r="F61" s="33" t="inlineStr"/>
+    </row>
+    <row r="62" ht="115" customHeight="1">
+      <c r="A62" s="33" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="33" t="inlineStr"/>
+      <c r="C62" s="33" t="inlineStr">
+        <is>
+          <t>df143b3a-image.jpg</t>
+        </is>
+      </c>
+      <c r="D62" s="33" t="inlineStr"/>
+      <c r="E62" s="33" t="inlineStr"/>
+      <c r="F62" s="33" t="inlineStr"/>
+    </row>
+    <row r="63" ht="115" customHeight="1">
+      <c r="A63" s="33" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="33" t="inlineStr"/>
+      <c r="C63" s="33" t="inlineStr">
+        <is>
+          <t>c6342b21-image.jpg</t>
+        </is>
+      </c>
+      <c r="D63" s="33" t="inlineStr"/>
+      <c r="E63" s="33" t="inlineStr"/>
+      <c r="F63" s="33" t="inlineStr"/>
+    </row>
+    <row r="64" ht="115" customHeight="1">
+      <c r="A64" s="33" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="33" t="inlineStr"/>
+      <c r="C64" s="33" t="inlineStr">
+        <is>
+          <t>86144c4f-image.jpg</t>
+        </is>
+      </c>
+      <c r="D64" s="33" t="inlineStr"/>
+      <c r="E64" s="33" t="inlineStr"/>
+      <c r="F64" s="33" t="inlineStr"/>
+    </row>
+    <row r="65" ht="115" customHeight="1">
+      <c r="A65" s="33" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="33" t="inlineStr"/>
+      <c r="C65" s="33" t="inlineStr">
+        <is>
+          <t>2c58ecc8-image.jpg</t>
+        </is>
+      </c>
+      <c r="D65" s="33" t="inlineStr"/>
+      <c r="E65" s="33" t="inlineStr"/>
+      <c r="F65" s="33" t="inlineStr"/>
+    </row>
+    <row r="66" ht="115" customHeight="1">
+      <c r="A66" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="33" t="inlineStr"/>
+      <c r="C66" s="33" t="inlineStr">
+        <is>
+          <t>7271b4de-image.jpg</t>
+        </is>
+      </c>
+      <c r="D66" s="33" t="inlineStr"/>
+      <c r="E66" s="33" t="inlineStr"/>
+      <c r="F66" s="33" t="inlineStr"/>
+    </row>
+    <row r="67" ht="115" customHeight="1">
+      <c r="A67" s="33" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="33" t="inlineStr"/>
+      <c r="C67" s="33" t="inlineStr">
+        <is>
+          <t>33722503-image.jpg</t>
+        </is>
+      </c>
+      <c r="D67" s="33" t="inlineStr"/>
+      <c r="E67" s="33" t="inlineStr"/>
+      <c r="F67" s="33" t="inlineStr"/>
+    </row>
+    <row r="68" ht="115" customHeight="1">
+      <c r="A68" s="33" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="33" t="inlineStr"/>
+      <c r="C68" s="33" t="inlineStr">
+        <is>
+          <t>a09636c1-image.jpg</t>
+        </is>
+      </c>
+      <c r="D68" s="33" t="inlineStr"/>
+      <c r="E68" s="33" t="inlineStr"/>
+      <c r="F68" s="33" t="inlineStr"/>
+    </row>
+    <row r="69" ht="115" customHeight="1">
+      <c r="A69" s="33" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="33" t="inlineStr"/>
+      <c r="C69" s="33" t="inlineStr">
+        <is>
+          <t>921349fd-image.jpg</t>
+        </is>
+      </c>
+      <c r="D69" s="33" t="inlineStr"/>
+      <c r="E69" s="33" t="inlineStr"/>
+      <c r="F69" s="33" t="inlineStr"/>
+    </row>
+    <row r="70" ht="115" customHeight="1">
+      <c r="A70" s="33" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="33" t="inlineStr"/>
+      <c r="C70" s="33" t="inlineStr">
+        <is>
+          <t>9c4d4db2-image.jpg</t>
+        </is>
+      </c>
+      <c r="D70" s="33" t="inlineStr"/>
+      <c r="E70" s="33" t="inlineStr"/>
+      <c r="F70" s="33" t="inlineStr"/>
+    </row>
+    <row r="71" ht="115" customHeight="1">
+      <c r="A71" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="33" t="inlineStr"/>
+      <c r="C71" s="33" t="inlineStr">
+        <is>
+          <t>38186c7b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D71" s="33" t="inlineStr"/>
+      <c r="E71" s="33" t="inlineStr"/>
+      <c r="F71" s="33" t="inlineStr"/>
+    </row>
+    <row r="72" ht="115" customHeight="1">
+      <c r="A72" s="33" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="33" t="inlineStr"/>
+      <c r="C72" s="33" t="inlineStr">
+        <is>
+          <t>273f5b3f-image.jpg</t>
+        </is>
+      </c>
+      <c r="D72" s="33" t="inlineStr"/>
+      <c r="E72" s="33" t="inlineStr"/>
+      <c r="F72" s="33" t="inlineStr"/>
+    </row>
+    <row r="73" ht="115" customHeight="1">
+      <c r="A73" s="33" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="33" t="inlineStr"/>
+      <c r="C73" s="33" t="inlineStr">
+        <is>
+          <t>e480464e-image.jpg</t>
+        </is>
+      </c>
+      <c r="D73" s="33" t="inlineStr"/>
+      <c r="E73" s="33" t="inlineStr"/>
+      <c r="F73" s="33" t="inlineStr"/>
+    </row>
+    <row r="74" ht="115" customHeight="1">
+      <c r="A74" s="33" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="33" t="inlineStr"/>
+      <c r="C74" s="33" t="inlineStr">
+        <is>
+          <t>46c2e4be-image.jpg</t>
+        </is>
+      </c>
+      <c r="D74" s="33" t="inlineStr"/>
+      <c r="E74" s="33" t="inlineStr"/>
+      <c r="F74" s="33" t="inlineStr"/>
+    </row>
+    <row r="75" ht="115" customHeight="1">
+      <c r="A75" s="33" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="33" t="inlineStr"/>
+      <c r="C75" s="33" t="inlineStr">
+        <is>
+          <t>8f555416-image.jpg</t>
+        </is>
+      </c>
+      <c r="D75" s="33" t="inlineStr"/>
+      <c r="E75" s="33" t="inlineStr"/>
+      <c r="F75" s="33" t="inlineStr"/>
+    </row>
+    <row r="76" ht="115" customHeight="1">
+      <c r="A76" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="33" t="inlineStr"/>
+      <c r="C76" s="33" t="inlineStr">
+        <is>
+          <t>6f640b59-image.jpg</t>
+        </is>
+      </c>
+      <c r="D76" s="33" t="inlineStr"/>
+      <c r="E76" s="33" t="inlineStr"/>
+      <c r="F76" s="33" t="inlineStr"/>
+    </row>
+    <row r="77" ht="115" customHeight="1">
+      <c r="A77" s="33" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="33" t="inlineStr"/>
+      <c r="C77" s="33" t="inlineStr">
+        <is>
+          <t>6ac90151-image.jpg</t>
+        </is>
+      </c>
+      <c r="D77" s="33" t="inlineStr"/>
+      <c r="E77" s="33" t="inlineStr"/>
+      <c r="F77" s="33" t="inlineStr"/>
+    </row>
+    <row r="78" ht="115" customHeight="1">
+      <c r="A78" s="33" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="33" t="inlineStr"/>
+      <c r="C78" s="33" t="inlineStr">
+        <is>
+          <t>a2aab3e3-image.jpg</t>
+        </is>
+      </c>
+      <c r="D78" s="33" t="inlineStr"/>
+      <c r="E78" s="33" t="inlineStr"/>
+      <c r="F78" s="33" t="inlineStr"/>
+    </row>
+    <row r="79" ht="115" customHeight="1">
+      <c r="A79" s="33" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="33" t="inlineStr"/>
+      <c r="C79" s="33" t="inlineStr">
+        <is>
+          <t>209d137d-image.jpg</t>
+        </is>
+      </c>
+      <c r="D79" s="33" t="inlineStr"/>
+      <c r="E79" s="33" t="inlineStr"/>
+      <c r="F79" s="33" t="inlineStr"/>
+    </row>
+    <row r="80" ht="115" customHeight="1">
+      <c r="A80" s="33" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="33" t="inlineStr"/>
+      <c r="C80" s="33" t="inlineStr">
+        <is>
+          <t>9b01acbd-image.jpg</t>
+        </is>
+      </c>
+      <c r="D80" s="33" t="inlineStr"/>
+      <c r="E80" s="33" t="inlineStr"/>
+      <c r="F80" s="33" t="inlineStr"/>
+    </row>
+    <row r="81" ht="115" customHeight="1">
+      <c r="A81" s="33" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="33" t="inlineStr"/>
+      <c r="C81" s="33" t="inlineStr">
+        <is>
+          <t>bc295bd0-image.jpg</t>
+        </is>
+      </c>
+      <c r="D81" s="33" t="inlineStr"/>
+      <c r="E81" s="33" t="inlineStr"/>
+      <c r="F81" s="33" t="inlineStr"/>
+    </row>
+    <row r="82" ht="115" customHeight="1">
+      <c r="A82" s="33" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="33" t="inlineStr"/>
+      <c r="C82" s="33" t="inlineStr">
+        <is>
+          <t>574837f2-image.jpg</t>
+        </is>
+      </c>
+      <c r="D82" s="33" t="inlineStr"/>
+      <c r="E82" s="33" t="inlineStr"/>
+      <c r="F82" s="33" t="inlineStr"/>
+    </row>
+    <row r="83" ht="115" customHeight="1">
+      <c r="A83" s="33" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="33" t="inlineStr"/>
+      <c r="C83" s="33" t="inlineStr">
+        <is>
+          <t>f20b51a4-image.jpg</t>
+        </is>
+      </c>
+      <c r="D83" s="33" t="inlineStr"/>
+      <c r="E83" s="33" t="inlineStr"/>
+      <c r="F83" s="33" t="inlineStr"/>
+    </row>
+    <row r="84" ht="115" customHeight="1">
+      <c r="A84" s="33" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="33" t="inlineStr"/>
+      <c r="C84" s="33" t="inlineStr">
+        <is>
+          <t>2095c232-image.jpg</t>
+        </is>
+      </c>
+      <c r="D84" s="33" t="inlineStr"/>
+      <c r="E84" s="33" t="inlineStr"/>
+      <c r="F84" s="33" t="inlineStr"/>
+    </row>
+    <row r="85" ht="115" customHeight="1">
+      <c r="A85" s="33" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="33" t="inlineStr"/>
+      <c r="C85" s="33" t="inlineStr">
+        <is>
+          <t>15749eac-image.jpg</t>
+        </is>
+      </c>
+      <c r="D85" s="33" t="inlineStr"/>
+      <c r="E85" s="33" t="inlineStr"/>
+      <c r="F85" s="33" t="inlineStr"/>
+    </row>
+    <row r="86" ht="115" customHeight="1">
+      <c r="A86" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="33" t="inlineStr"/>
+      <c r="C86" s="33" t="inlineStr">
+        <is>
+          <t>0528c5a3-image.jpg</t>
+        </is>
+      </c>
+      <c r="D86" s="33" t="inlineStr"/>
+      <c r="E86" s="33" t="inlineStr"/>
+      <c r="F86" s="33" t="inlineStr"/>
+    </row>
+    <row r="87" ht="115" customHeight="1">
+      <c r="A87" s="33" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="33" t="inlineStr"/>
+      <c r="C87" s="33" t="inlineStr">
+        <is>
+          <t>2a7795f9-image.jpg</t>
+        </is>
+      </c>
+      <c r="D87" s="33" t="inlineStr"/>
+      <c r="E87" s="33" t="inlineStr"/>
+      <c r="F87" s="33" t="inlineStr"/>
+    </row>
+    <row r="88" ht="115" customHeight="1">
+      <c r="A88" s="33" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="33" t="inlineStr"/>
+      <c r="C88" s="33" t="inlineStr">
+        <is>
+          <t>c9df70e8-image.jpg</t>
+        </is>
+      </c>
+      <c r="D88" s="33" t="inlineStr"/>
+      <c r="E88" s="33" t="inlineStr"/>
+      <c r="F88" s="33" t="inlineStr"/>
+    </row>
+    <row r="89" ht="115" customHeight="1">
+      <c r="A89" s="33" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="33" t="inlineStr"/>
+      <c r="C89" s="33" t="inlineStr">
+        <is>
+          <t>ed0e87c5-image.jpg</t>
+        </is>
+      </c>
+      <c r="D89" s="33" t="inlineStr"/>
+      <c r="E89" s="33" t="inlineStr"/>
+      <c r="F89" s="33" t="inlineStr"/>
+    </row>
+    <row r="90" ht="115" customHeight="1">
+      <c r="A90" s="33" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="33" t="inlineStr"/>
+      <c r="C90" s="33" t="inlineStr">
+        <is>
+          <t>23d75300-image.jpg</t>
+        </is>
+      </c>
+      <c r="D90" s="33" t="inlineStr"/>
+      <c r="E90" s="33" t="inlineStr"/>
+      <c r="F90" s="33" t="inlineStr"/>
+    </row>
+    <row r="91" ht="115" customHeight="1">
+      <c r="A91" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="33" t="inlineStr"/>
+      <c r="C91" s="33" t="inlineStr">
+        <is>
+          <t>10391572-image.jpg</t>
+        </is>
+      </c>
+      <c r="D91" s="33" t="inlineStr"/>
+      <c r="E91" s="33" t="inlineStr"/>
+      <c r="F91" s="33" t="inlineStr"/>
+    </row>
+    <row r="92" ht="115" customHeight="1">
+      <c r="A92" s="33" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="33" t="inlineStr"/>
+      <c r="C92" s="33" t="inlineStr">
+        <is>
+          <t>916567be-image.jpg</t>
+        </is>
+      </c>
+      <c r="D92" s="33" t="inlineStr"/>
+      <c r="E92" s="33" t="inlineStr"/>
+      <c r="F92" s="33" t="inlineStr"/>
+    </row>
+    <row r="93" ht="115" customHeight="1">
+      <c r="A93" s="33" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="33" t="inlineStr"/>
+      <c r="C93" s="33" t="inlineStr">
+        <is>
+          <t>ee4ae134-image.jpg</t>
+        </is>
+      </c>
+      <c r="D93" s="33" t="inlineStr"/>
+      <c r="E93" s="33" t="inlineStr"/>
+      <c r="F93" s="33" t="inlineStr"/>
+    </row>
+    <row r="94" ht="115" customHeight="1">
+      <c r="A94" s="33" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="33" t="inlineStr"/>
+      <c r="C94" s="33" t="inlineStr">
+        <is>
+          <t>03d3c90a-image.jpg</t>
+        </is>
+      </c>
+      <c r="D94" s="33" t="inlineStr"/>
+      <c r="E94" s="33" t="inlineStr"/>
+      <c r="F94" s="33" t="inlineStr"/>
+    </row>
+    <row r="95" ht="115" customHeight="1">
+      <c r="A95" s="33" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="33" t="inlineStr"/>
+      <c r="C95" s="33" t="inlineStr">
+        <is>
+          <t>3f8eb293-image.jpg</t>
+        </is>
+      </c>
+      <c r="D95" s="33" t="inlineStr"/>
+      <c r="E95" s="33" t="inlineStr"/>
+      <c r="F95" s="33" t="inlineStr"/>
+    </row>
+    <row r="96" ht="115" customHeight="1">
+      <c r="A96" s="33" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="33" t="inlineStr"/>
+      <c r="C96" s="33" t="inlineStr">
+        <is>
+          <t>c8642d34-image.jpg</t>
+        </is>
+      </c>
+      <c r="D96" s="33" t="inlineStr"/>
+      <c r="E96" s="33" t="inlineStr"/>
+      <c r="F96" s="33" t="inlineStr"/>
+    </row>
+    <row r="97" ht="115" customHeight="1">
+      <c r="A97" s="33" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="33" t="inlineStr"/>
+      <c r="C97" s="33" t="inlineStr">
+        <is>
+          <t>13ad7167-image.jpg</t>
+        </is>
+      </c>
+      <c r="D97" s="33" t="inlineStr"/>
+      <c r="E97" s="33" t="inlineStr"/>
+      <c r="F97" s="33" t="inlineStr"/>
+    </row>
+    <row r="98" ht="115" customHeight="1">
+      <c r="A98" s="33" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="33" t="inlineStr"/>
+      <c r="C98" s="33" t="inlineStr">
+        <is>
+          <t>c06c08e1-image.jpg</t>
+        </is>
+      </c>
+      <c r="D98" s="33" t="inlineStr"/>
+      <c r="E98" s="33" t="inlineStr"/>
+      <c r="F98" s="33" t="inlineStr"/>
+    </row>
+    <row r="99" ht="115" customHeight="1">
+      <c r="A99" s="33" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="33" t="inlineStr"/>
+      <c r="C99" s="33" t="inlineStr">
+        <is>
+          <t>a49fcbea-image.jpg</t>
+        </is>
+      </c>
+      <c r="D99" s="33" t="inlineStr"/>
+      <c r="E99" s="33" t="inlineStr"/>
+      <c r="F99" s="33" t="inlineStr"/>
+    </row>
+    <row r="100" ht="115" customHeight="1">
+      <c r="A100" s="33" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="33" t="inlineStr"/>
+      <c r="C100" s="33" t="inlineStr">
+        <is>
+          <t>7f8e1ee5-image.jpg</t>
+        </is>
+      </c>
+      <c r="D100" s="33" t="inlineStr"/>
+      <c r="E100" s="33" t="inlineStr"/>
+      <c r="F100" s="33" t="inlineStr"/>
+    </row>
+    <row r="101" ht="115" customHeight="1">
+      <c r="A101" s="33" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="33" t="inlineStr"/>
+      <c r="C101" s="33" t="inlineStr">
+        <is>
+          <t>deaad37c-image.jpg</t>
+        </is>
+      </c>
+      <c r="D101" s="33" t="inlineStr"/>
+      <c r="E101" s="33" t="inlineStr"/>
+      <c r="F101" s="33" t="inlineStr"/>
+    </row>
+    <row r="102" ht="115" customHeight="1">
+      <c r="A102" s="33" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="33" t="inlineStr"/>
+      <c r="C102" s="33" t="inlineStr">
+        <is>
+          <t>2f500f56-image.jpg</t>
+        </is>
+      </c>
+      <c r="D102" s="33" t="inlineStr"/>
+      <c r="E102" s="33" t="inlineStr"/>
+      <c r="F102" s="33" t="inlineStr"/>
+    </row>
+    <row r="103" ht="115" customHeight="1">
+      <c r="A103" s="33" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="33" t="inlineStr"/>
+      <c r="C103" s="33" t="inlineStr">
+        <is>
+          <t>2c09ba62-image.jpg</t>
+        </is>
+      </c>
+      <c r="D103" s="33" t="inlineStr"/>
+      <c r="E103" s="33" t="inlineStr"/>
+      <c r="F103" s="33" t="inlineStr"/>
+    </row>
+    <row r="104" ht="115" customHeight="1">
+      <c r="A104" s="33" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="33" t="inlineStr"/>
+      <c r="C104" s="33" t="inlineStr">
+        <is>
+          <t>333b4578-image.jpg</t>
+        </is>
+      </c>
+      <c r="D104" s="33" t="inlineStr"/>
+      <c r="E104" s="33" t="inlineStr"/>
+      <c r="F104" s="33" t="inlineStr"/>
+    </row>
+    <row r="105" ht="115" customHeight="1">
+      <c r="A105" s="33" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="33" t="inlineStr"/>
+      <c r="C105" s="33" t="inlineStr">
+        <is>
+          <t>810e0128-image.jpg</t>
+        </is>
+      </c>
+      <c r="D105" s="33" t="inlineStr"/>
+      <c r="E105" s="33" t="inlineStr"/>
+      <c r="F105" s="33" t="inlineStr"/>
+    </row>
+    <row r="106" ht="115" customHeight="1">
+      <c r="A106" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="33" t="inlineStr"/>
+      <c r="C106" s="33" t="inlineStr">
+        <is>
+          <t>79f40265-image.jpg</t>
+        </is>
+      </c>
+      <c r="D106" s="33" t="inlineStr"/>
+      <c r="E106" s="33" t="inlineStr"/>
+      <c r="F106" s="33" t="inlineStr"/>
+    </row>
+    <row r="107" ht="115" customHeight="1">
+      <c r="A107" s="33" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="33" t="inlineStr"/>
+      <c r="C107" s="33" t="inlineStr">
+        <is>
+          <t>ab155988-image.jpg</t>
+        </is>
+      </c>
+      <c r="D107" s="33" t="inlineStr"/>
+      <c r="E107" s="33" t="inlineStr"/>
+      <c r="F107" s="33" t="inlineStr"/>
+    </row>
+    <row r="108" ht="115" customHeight="1">
+      <c r="A108" s="33" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="33" t="inlineStr"/>
+      <c r="C108" s="33" t="inlineStr">
+        <is>
+          <t>a1bc497b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D108" s="33" t="inlineStr"/>
+      <c r="E108" s="33" t="inlineStr"/>
+      <c r="F108" s="33" t="inlineStr"/>
+    </row>
+    <row r="109" ht="115" customHeight="1">
+      <c r="A109" s="33" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="33" t="inlineStr"/>
+      <c r="C109" s="33" t="inlineStr">
+        <is>
+          <t>ff9a6516-image.jpg</t>
+        </is>
+      </c>
+      <c r="D109" s="33" t="inlineStr"/>
+      <c r="E109" s="33" t="inlineStr"/>
+      <c r="F109" s="33" t="inlineStr"/>
+    </row>
+    <row r="110" ht="115" customHeight="1">
+      <c r="A110" s="33" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="33" t="inlineStr"/>
+      <c r="C110" s="33" t="inlineStr">
+        <is>
+          <t>5dd2093e-image.jpg</t>
+        </is>
+      </c>
+      <c r="D110" s="33" t="inlineStr"/>
+      <c r="E110" s="33" t="inlineStr"/>
+      <c r="F110" s="33" t="inlineStr"/>
+    </row>
+    <row r="111" ht="115" customHeight="1">
+      <c r="A111" s="33" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="33" t="inlineStr"/>
+      <c r="C111" s="33" t="inlineStr">
+        <is>
+          <t>7028a05a-image.jpg</t>
+        </is>
+      </c>
+      <c r="D111" s="33" t="inlineStr"/>
+      <c r="E111" s="33" t="inlineStr"/>
+      <c r="F111" s="33" t="inlineStr"/>
+    </row>
+    <row r="112" ht="115" customHeight="1">
+      <c r="A112" s="33" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="33" t="inlineStr"/>
+      <c r="C112" s="33" t="inlineStr">
+        <is>
+          <t>415a2218-image.jpg</t>
+        </is>
+      </c>
+      <c r="D112" s="33" t="inlineStr"/>
+      <c r="E112" s="33" t="inlineStr"/>
+      <c r="F112" s="33" t="inlineStr"/>
+    </row>
+    <row r="113" ht="115" customHeight="1">
+      <c r="A113" s="33" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="33" t="inlineStr"/>
+      <c r="C113" s="33" t="inlineStr">
+        <is>
+          <t>0a2a6c8a-image.jpg</t>
+        </is>
+      </c>
+      <c r="D113" s="33" t="inlineStr"/>
+      <c r="E113" s="33" t="inlineStr"/>
+      <c r="F113" s="33" t="inlineStr"/>
+    </row>
+    <row r="114" ht="115" customHeight="1">
+      <c r="A114" s="33" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="33" t="inlineStr"/>
+      <c r="C114" s="33" t="inlineStr">
+        <is>
+          <t>fe4b2d0a-image.jpg</t>
+        </is>
+      </c>
+      <c r="D114" s="33" t="inlineStr"/>
+      <c r="E114" s="33" t="inlineStr"/>
+      <c r="F114" s="33" t="inlineStr"/>
+    </row>
+    <row r="115" ht="115" customHeight="1">
+      <c r="A115" s="33" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="33" t="inlineStr"/>
+      <c r="C115" s="33" t="inlineStr">
+        <is>
+          <t>9c511218-image.jpg</t>
+        </is>
+      </c>
+      <c r="D115" s="33" t="inlineStr"/>
+      <c r="E115" s="33" t="inlineStr"/>
+      <c r="F115" s="33" t="inlineStr"/>
+    </row>
+    <row r="116" ht="115" customHeight="1">
+      <c r="A116" s="33" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="33" t="inlineStr"/>
+      <c r="C116" s="33" t="inlineStr">
+        <is>
+          <t>3dc15c23-image.jpg</t>
+        </is>
+      </c>
+      <c r="D116" s="33" t="inlineStr"/>
+      <c r="E116" s="33" t="inlineStr"/>
+      <c r="F116" s="33" t="inlineStr"/>
+    </row>
+    <row r="117" ht="115" customHeight="1">
+      <c r="A117" s="33" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="33" t="inlineStr"/>
+      <c r="C117" s="33" t="inlineStr">
+        <is>
+          <t>89717e55-image.jpg</t>
+        </is>
+      </c>
+      <c r="D117" s="33" t="inlineStr"/>
+      <c r="E117" s="33" t="inlineStr"/>
+      <c r="F117" s="33" t="inlineStr"/>
+    </row>
+    <row r="118" ht="115" customHeight="1">
+      <c r="A118" s="33" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="33" t="inlineStr"/>
+      <c r="C118" s="33" t="inlineStr">
+        <is>
+          <t>43154a1b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D118" s="33" t="inlineStr"/>
+      <c r="E118" s="33" t="inlineStr"/>
+      <c r="F118" s="33" t="inlineStr"/>
+    </row>
+    <row r="119" ht="115" customHeight="1">
+      <c r="A119" s="33" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="33" t="inlineStr"/>
+      <c r="C119" s="33" t="inlineStr">
+        <is>
+          <t>d3a8bd76-image.jpg</t>
+        </is>
+      </c>
+      <c r="D119" s="33" t="inlineStr"/>
+      <c r="E119" s="33" t="inlineStr"/>
+      <c r="F119" s="33" t="inlineStr"/>
+    </row>
+    <row r="120" ht="115" customHeight="1">
+      <c r="A120" s="33" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="33" t="inlineStr"/>
+      <c r="C120" s="33" t="inlineStr">
+        <is>
+          <t>6b05a641-image.jpg</t>
+        </is>
+      </c>
+      <c r="D120" s="33" t="inlineStr"/>
+      <c r="E120" s="33" t="inlineStr"/>
+      <c r="F120" s="33" t="inlineStr"/>
+    </row>
+    <row r="121" ht="115" customHeight="1">
+      <c r="A121" s="33" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="33" t="inlineStr"/>
+      <c r="C121" s="33" t="inlineStr">
+        <is>
+          <t>cada4195-image.jpg</t>
+        </is>
+      </c>
+      <c r="D121" s="33" t="inlineStr"/>
+      <c r="E121" s="33" t="inlineStr"/>
+      <c r="F121" s="33" t="inlineStr"/>
+    </row>
+    <row r="122" ht="115" customHeight="1">
+      <c r="A122" s="33" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="33" t="inlineStr"/>
+      <c r="C122" s="33" t="inlineStr">
+        <is>
+          <t>6a05ec04-image.jpg</t>
+        </is>
+      </c>
+      <c r="D122" s="33" t="inlineStr"/>
+      <c r="E122" s="33" t="inlineStr"/>
+      <c r="F122" s="33" t="inlineStr"/>
+    </row>
+    <row r="123" ht="115" customHeight="1">
+      <c r="A123" s="33" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="33" t="inlineStr"/>
+      <c r="C123" s="33" t="inlineStr">
+        <is>
+          <t>b64e6828-image.jpg</t>
+        </is>
+      </c>
+      <c r="D123" s="33" t="inlineStr"/>
+      <c r="E123" s="33" t="inlineStr"/>
+      <c r="F123" s="33" t="inlineStr"/>
+    </row>
+    <row r="124" ht="115" customHeight="1">
+      <c r="A124" s="33" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="33" t="inlineStr"/>
+      <c r="C124" s="33" t="inlineStr">
+        <is>
+          <t>1d8798e9-image.jpg</t>
+        </is>
+      </c>
+      <c r="D124" s="33" t="inlineStr"/>
+      <c r="E124" s="33" t="inlineStr"/>
+      <c r="F124" s="33" t="inlineStr"/>
+    </row>
+    <row r="125" ht="115" customHeight="1">
+      <c r="A125" s="33" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="33" t="inlineStr"/>
+      <c r="C125" s="33" t="inlineStr">
+        <is>
+          <t>97481ad4-image.jpg</t>
+        </is>
+      </c>
+      <c r="D125" s="33" t="inlineStr"/>
+      <c r="E125" s="33" t="inlineStr"/>
+      <c r="F125" s="33" t="inlineStr"/>
+    </row>
+    <row r="126" ht="115" customHeight="1">
+      <c r="A126" s="33" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="33" t="inlineStr"/>
+      <c r="C126" s="33" t="inlineStr">
+        <is>
+          <t>915274ff-image.jpg</t>
+        </is>
+      </c>
+      <c r="D126" s="33" t="inlineStr"/>
+      <c r="E126" s="33" t="inlineStr"/>
+      <c r="F126" s="33" t="inlineStr"/>
+    </row>
+    <row r="127" ht="115" customHeight="1">
+      <c r="A127" s="33" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="33" t="inlineStr"/>
+      <c r="C127" s="33" t="inlineStr">
+        <is>
+          <t>bbad6f56-image.jpg</t>
+        </is>
+      </c>
+      <c r="D127" s="33" t="inlineStr"/>
+      <c r="E127" s="33" t="inlineStr"/>
+      <c r="F127" s="33" t="inlineStr"/>
+    </row>
+    <row r="128" ht="115" customHeight="1">
+      <c r="A128" s="33" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="33" t="inlineStr"/>
+      <c r="C128" s="33" t="inlineStr">
+        <is>
+          <t>ee98a2e0-image.jpg</t>
+        </is>
+      </c>
+      <c r="D128" s="33" t="inlineStr"/>
+      <c r="E128" s="33" t="inlineStr"/>
+      <c r="F128" s="33" t="inlineStr"/>
+    </row>
+    <row r="129" ht="115" customHeight="1">
+      <c r="A129" s="33" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="33" t="inlineStr"/>
+      <c r="C129" s="33" t="inlineStr">
+        <is>
+          <t>1f250e5b-image.jpg</t>
+        </is>
+      </c>
+      <c r="D129" s="33" t="inlineStr"/>
+      <c r="E129" s="33" t="inlineStr"/>
+      <c r="F129" s="33" t="inlineStr"/>
+    </row>
+    <row r="130" ht="115" customHeight="1">
+      <c r="A130" s="33" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="33" t="inlineStr"/>
+      <c r="C130" s="33" t="inlineStr">
+        <is>
+          <t>f9774cd7-image.jpg</t>
+        </is>
+      </c>
+      <c r="D130" s="33" t="inlineStr"/>
+      <c r="E130" s="33" t="inlineStr"/>
+      <c r="F130" s="33" t="inlineStr"/>
+    </row>
+    <row r="131" ht="115" customHeight="1">
+      <c r="A131" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="33" t="inlineStr"/>
+      <c r="C131" s="33" t="inlineStr">
+        <is>
+          <t>6f1cb085-image.jpg</t>
+        </is>
+      </c>
+      <c r="D131" s="33" t="inlineStr"/>
+      <c r="E131" s="33" t="inlineStr"/>
+      <c r="F131" s="33" t="inlineStr"/>
+    </row>
+    <row r="132" ht="115" customHeight="1">
+      <c r="A132" s="33" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="33" t="inlineStr"/>
+      <c r="C132" s="33" t="inlineStr">
+        <is>
+          <t>bc8d9b40-image.jpg</t>
+        </is>
+      </c>
+      <c r="D132" s="33" t="inlineStr"/>
+      <c r="E132" s="33" t="inlineStr"/>
+      <c r="F132" s="33" t="inlineStr"/>
+    </row>
+    <row r="133" ht="115" customHeight="1">
+      <c r="A133" s="33" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="33" t="inlineStr"/>
+      <c r="C133" s="33" t="inlineStr">
+        <is>
+          <t>b3148cf5-image.jpg</t>
+        </is>
+      </c>
+      <c r="D133" s="33" t="inlineStr"/>
+      <c r="E133" s="33" t="inlineStr"/>
+      <c r="F133" s="33" t="inlineStr"/>
+    </row>
+    <row r="134" ht="115" customHeight="1">
+      <c r="A134" s="33" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="33" t="inlineStr"/>
+      <c r="C134" s="33" t="inlineStr">
+        <is>
+          <t>71d98caa-image.jpg</t>
+        </is>
+      </c>
+      <c r="D134" s="33" t="inlineStr"/>
+      <c r="E134" s="33" t="inlineStr"/>
+      <c r="F134" s="33" t="inlineStr"/>
+    </row>
+    <row r="135" ht="115" customHeight="1">
+      <c r="A135" s="33" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="33" t="inlineStr"/>
+      <c r="C135" s="33" t="inlineStr">
+        <is>
+          <t>24a5fe80-image.jpg</t>
+        </is>
+      </c>
+      <c r="D135" s="33" t="inlineStr"/>
+      <c r="E135" s="33" t="inlineStr"/>
+      <c r="F135" s="33" t="inlineStr"/>
+    </row>
+    <row r="136" ht="115" customHeight="1">
+      <c r="A136" s="33" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="33" t="inlineStr"/>
+      <c r="C136" s="33" t="inlineStr">
+        <is>
+          <t>393f3d0f-image.jpg</t>
+        </is>
+      </c>
+      <c r="D136" s="33" t="inlineStr"/>
+      <c r="E136" s="33" t="inlineStr"/>
+      <c r="F136" s="33" t="inlineStr"/>
+    </row>
+    <row r="137" ht="115" customHeight="1">
+      <c r="A137" s="33" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="33" t="inlineStr"/>
+      <c r="C137" s="33" t="inlineStr">
+        <is>
+          <t>e670839d-image.jpg</t>
+        </is>
+      </c>
+      <c r="D137" s="33" t="inlineStr"/>
+      <c r="E137" s="33" t="inlineStr"/>
+      <c r="F137" s="33" t="inlineStr"/>
+    </row>
+    <row r="138" ht="115" customHeight="1">
+      <c r="A138" s="33" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="33" t="inlineStr"/>
+      <c r="C138" s="33" t="inlineStr">
+        <is>
+          <t>6b4002db-image.jpg</t>
+        </is>
+      </c>
+      <c r="D138" s="33" t="inlineStr"/>
+      <c r="E138" s="33" t="inlineStr"/>
+      <c r="F138" s="33" t="inlineStr"/>
+    </row>
+    <row r="139" ht="115" customHeight="1">
+      <c r="A139" s="33" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="33" t="inlineStr"/>
+      <c r="C139" s="33" t="inlineStr">
+        <is>
+          <t>1c7cdc73-image.jpg</t>
+        </is>
+      </c>
+      <c r="D139" s="33" t="inlineStr"/>
+      <c r="E139" s="33" t="inlineStr"/>
+      <c r="F139" s="33" t="inlineStr"/>
+    </row>
+    <row r="140" ht="115" customHeight="1">
+      <c r="A140" s="33" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="33" t="inlineStr"/>
+      <c r="C140" s="33" t="inlineStr">
+        <is>
+          <t>a19d91f9-image.jpg</t>
+        </is>
+      </c>
+      <c r="D140" s="33" t="inlineStr"/>
+      <c r="E140" s="33" t="inlineStr"/>
+      <c r="F140" s="33" t="inlineStr"/>
+    </row>
+    <row r="141" ht="115" customHeight="1">
+      <c r="A141" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="33" t="inlineStr"/>
+      <c r="C141" s="33" t="inlineStr">
+        <is>
+          <t>62bf6f0f-image.jpg</t>
+        </is>
+      </c>
+      <c r="D141" s="33" t="inlineStr"/>
+      <c r="E141" s="33" t="inlineStr"/>
+      <c r="F141" s="33" t="inlineStr"/>
+    </row>
+    <row r="142" ht="115" customHeight="1">
+      <c r="A142" s="33" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="33" t="inlineStr"/>
+      <c r="C142" s="33" t="inlineStr">
+        <is>
+          <t>b14dd9af-image.jpg</t>
+        </is>
+      </c>
+      <c r="D142" s="33" t="inlineStr"/>
+      <c r="E142" s="33" t="inlineStr"/>
+      <c r="F142" s="33" t="inlineStr"/>
+    </row>
+    <row r="143" ht="115" customHeight="1">
+      <c r="A143" s="33" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="33" t="inlineStr"/>
+      <c r="C143" s="33" t="inlineStr">
+        <is>
+          <t>9e543440-image.jpg</t>
+        </is>
+      </c>
+      <c r="D143" s="33" t="inlineStr"/>
+      <c r="E143" s="33" t="inlineStr"/>
+      <c r="F143" s="33" t="inlineStr"/>
+    </row>
+    <row r="144" ht="115" customHeight="1">
+      <c r="A144" s="33" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="33" t="inlineStr"/>
+      <c r="C144" s="33" t="inlineStr">
+        <is>
+          <t>09df03a4-image.jpg</t>
+        </is>
+      </c>
+      <c r="D144" s="33" t="inlineStr"/>
+      <c r="E144" s="33" t="inlineStr"/>
+      <c r="F144" s="33" t="inlineStr"/>
+    </row>
+    <row r="145" ht="115" customHeight="1">
+      <c r="A145" s="33" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="33" t="inlineStr"/>
+      <c r="C145" s="33" t="inlineStr">
+        <is>
+          <t>01192393-image.jpg</t>
+        </is>
+      </c>
+      <c r="D145" s="33" t="inlineStr"/>
+      <c r="E145" s="33" t="inlineStr"/>
+      <c r="F145" s="33" t="inlineStr"/>
+    </row>
+    <row r="146" ht="115" customHeight="1">
+      <c r="A146" s="33" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="33" t="inlineStr"/>
+      <c r="C146" s="33" t="inlineStr">
+        <is>
+          <t>c2a96fb2-image.jpg</t>
+        </is>
+      </c>
+      <c r="D146" s="33" t="inlineStr"/>
+      <c r="E146" s="33" t="inlineStr"/>
+      <c r="F146" s="33" t="inlineStr"/>
+    </row>
+    <row r="147" ht="115" customHeight="1">
+      <c r="A147" s="33" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="33" t="inlineStr"/>
+      <c r="C147" s="33" t="inlineStr">
+        <is>
+          <t>8deee0dd-image.jpg</t>
+        </is>
+      </c>
+      <c r="D147" s="33" t="inlineStr"/>
+      <c r="E147" s="33" t="inlineStr"/>
+      <c r="F147" s="33" t="inlineStr"/>
+    </row>
+    <row r="148" ht="115" customHeight="1">
+      <c r="A148" s="33" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="33" t="inlineStr"/>
+      <c r="C148" s="33" t="inlineStr">
+        <is>
+          <t>4f05d94d-image.jpg</t>
+        </is>
+      </c>
+      <c r="D148" s="33" t="inlineStr"/>
+      <c r="E148" s="33" t="inlineStr"/>
+      <c r="F148" s="33" t="inlineStr"/>
+    </row>
+    <row r="149" ht="115" customHeight="1">
+      <c r="A149" s="33" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="33" t="inlineStr"/>
+      <c r="C149" s="33" t="inlineStr">
+        <is>
+          <t>00396226-image.jpg</t>
+        </is>
+      </c>
+      <c r="D149" s="33" t="inlineStr"/>
+      <c r="E149" s="33" t="inlineStr"/>
+      <c r="F149" s="33" t="inlineStr"/>
+    </row>
+    <row r="150" ht="115" customHeight="1">
+      <c r="A150" s="33" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="33" t="inlineStr"/>
+      <c r="C150" s="33" t="inlineStr">
+        <is>
+          <t>98821ce0-image.jpg</t>
+        </is>
+      </c>
+      <c r="D150" s="33" t="inlineStr"/>
+      <c r="E150" s="33" t="inlineStr"/>
+      <c r="F150" s="33" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>